--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_666_Saint_Pierre_Miquelon_France.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_666_Saint_Pierre_Miquelon_France.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc2ff7a498db74975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R53576f4d41224b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R94f397b81e04439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd5fe881e612342a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R98433c170d404e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R64cc8a0d1e8d4dbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R44025067b6aa43d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9e1ae940e9e84fa8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R819fd5326e1c47a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5cf657d90b5541d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R53bed9b5bcc64ae7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R12844cd4c90c40a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ666CommercialTable" displayName="EEZ666CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ666CommercialTable" displayName="EEZ666CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ666FunctionalTable" displayName="EEZ666FunctionalTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ666FunctionalTable" displayName="EEZ666FunctionalTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ666ValidationTable" displayName="EEZ666ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ666ValidationTable" displayName="EEZ666ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -2101,7 +2055,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc18eac5b768646fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R372e1bc7c6b04040"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2111,20 +2065,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2132,552 +2076,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>106.2902612797</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.100512836327662</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1260.4128910358659</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>106.2902612797</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1272.7332886346965</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$22,A2,'Species'!$U$2:$U$22))</x:f>
-        <x:v>135279.15378835372</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.100512836327662</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1260.4128910358659</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>133969.61550850424</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1309.538279849483</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0097748901859493</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.009774890185949327</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>96.309614689</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.5879455901562385</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>387.20913104683905</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>96.309614689</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>393.01944277234446</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$22,A3,'Species'!$U$2:$U$22))</x:f>
-        <x:v>37851.55109868998</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.5879455901562385</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>387.20913104683905</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>37291.96221518358</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>559.5888835064034</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0150056164992725</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.015005616499272446</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>28.103895135600002</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.8695157488065144</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>740.4841191152954</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>28.103895135600002</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>857.8207365687488</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$22,A4,'Species'!$U$2:$U$22))</x:f>
-        <x:v>24108.10402567127</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.8695157488065144</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>740.4841191152954</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20810.4880331934</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3297.6159924778694</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1584593300848143</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.15845933008481422</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>7.5272727281</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>7.5272727281</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$22,A5,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1088.0219366446938</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>1088.0219366446938</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>88.9793421257</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.615731455283818</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>41.279217423026886</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>88.9793421257</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>127.56228425538373</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$22,A6,'Species'!$U$2:$U$22))</x:f>
-        <x:v>11350.408133095583</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.615731455283818</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>41.279217423026886</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3672.9976097646654</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>7677.410523330918</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>3.090230198604137</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>2.090230198604137</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1281.7246435798997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.294021349835414</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>196.7983033006305</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1281.7246435798997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>208.5609985642352</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$22,A7,'Species'!$U$2:$U$22))</x:f>
-        <x:v>267317.77154941234</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.294021349835414</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>196.7983033006305</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>252241.23515512963</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>15076.53639428271</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0597703083122416</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.05977030831224151</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22.5780545465</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.493397232835408</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>311.4563809094669</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22.5780545465</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>692.5442094712464</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$22,A8,'Species'!$U$2:$U$22))</x:f>
-        <x:v>15636.300937304522</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.493397232835408</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>311.4563809094669</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>7032.079157029424</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>8604.221780275098</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.223567253459331</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.2235672534593307</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>13.1122026454</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.378874589659642</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>239.2624743224435</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>13.1122026454</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>653.4282779959451</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$22,A9,'Species'!$U$2:$U$22))</x:f>
-        <x:v>8567.883995317598</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.378874589659642</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>239.2624743224435</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3137.2580487556934</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>5430.625946561904</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.731010284192533</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.731010284192533</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>121.4613317921</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.78</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>602.5595860743575</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>121.4613317921</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$22,A10,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>73187.68980868798</x:v>
       </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.78</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>73187.68980868798</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4bb566248d24421"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc19eab7a05914e65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2687,20 +2272,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2708,660 +2283,231 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>22.4484176395</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.080569105088392</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1203.840930137618</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>22.4484176395</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1219.1341870712715</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$22,A2,'Species'!$U$2:$U$22))</x:f>
-        <x:v>27367.633389968225</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.080569105088392</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1203.840930137618</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>27024.32397125339</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>343.30941871483446</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0127037190303085</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.012703719030308522</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>95.4593813746</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.099547830573335</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1257.615352906272</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>95.4593813746</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1275.2602184751788</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$22,A3,'Species'!$U$2:$U$22))</x:f>
-        <x:v>121735.55154727782</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.099547830573335</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1257.615352906272</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>120051.18359563198</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1684.367951645836</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.014030415204562</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.01403041520456214</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6.788017551299999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.31</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2041.7379446695275</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6.788017551299999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2041.7379446695275</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$22,A4,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>13859.35300357194</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.31</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2041.7379446695275</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>13859.35300357194</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>23.25</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1000</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>23.25</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$22,A5,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>23250</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>23250</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>15.0507818196</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>15.0507818196</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$22,A6,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1938.9162931730866</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1938.9162931730866</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>96.309614689</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5879455901562385</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>387.20913104683905</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>96.309614689</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>393.01944277234446</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$22,A7,'Species'!$U$2:$U$22))</x:f>
-        <x:v>37851.55109868998</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5879455901562385</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>387.20913104683905</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>37291.96221518358</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>559.5888835064034</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0150056164992725</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.015005616499272446</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1387.0034200863</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.327173685164618</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>212.4093770086018</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1387.0034200863</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>230.6063675201962</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$22,A8,'Species'!$U$2:$U$22))</x:f>
-        <x:v>319851.82044419035</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.327173685164618</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>212.4093770086018</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>294612.532369331</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>25239.28807485936</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0856694312081028</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0856694312081028</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>7.527272726900001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.26</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1819.7008586099826</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>7.527272726900001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1819.7008586099826</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$22,A9,'Species'!$U$2:$U$22))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>13697.384644131436</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.26</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1819.7008586099826</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>13697.384644131436</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>88.9793421257</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.615731455283818</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>41.279217423026886</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>88.9793421257</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>127.56228425538373</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$22,A10,'Species'!$U$2:$U$22))</x:f>
-        <x:v>11350.408133095583</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.615731455283818</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>41.279217423026886</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>3672.9976097646654</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7677.410523330918</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>3.090230198604137</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>2.090230198604137</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>18.4164753735</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.1540872493652783</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>142.58940256383974</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>18.4164753735</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>142.59855049065723</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$22,A11,'Species'!$U$2:$U$22))</x:f>
-        <x:v>2626.162693407985</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.1540872493652783</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>142.58940256383974</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2625.994220839032</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.1684725689528932</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000064155727235</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.00006415572723502205</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>4.8538951356</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2445004249281744</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>175.59026122318556</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>4.8538951356</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>176.786684033955</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$22,A12,'Species'!$U$2:$U$22))</x:f>
-        <x:v>858.1040256712683</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2445004249281744</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>175.59026122318556</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>852.2967148099538</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>5.8073108613145905</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.006813719635901</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.006813719635901111</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6411ceef800246e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R885d468f57714643"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3536,7 +2682,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -3635,7 +2781,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>574386.8852731778</x:v>
+        <x:v>532431.3474728933</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3649,7 +2795,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>574386.8852731776</x:v>
+        <x:v>538876.9446376901</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3663,7 +2809,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1641532182693481e-10</x:v>
+        <x:v>-41955.53780028457</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3677,7 +2823,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.3283064365386963e-10</x:v>
+        <x:v>-35509.94063548779</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3688,9 +2834,9 @@
         <x:v>EEZ_666</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -3702,47 +2848,19 @@
         <x:v>EEZ_666</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_666</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_666</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb76c593635e8467e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57155d015e904f6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3789,7 +2907,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
